--- a/DCS_Missions/DCS_Maps/Kola/Base/Kneeboards/presets.xlsx
+++ b/DCS_Missions/DCS_Maps/Kola/Base/Kneeboards/presets.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\repo\DCS\DCS_Missions\DCS_Maps\Kola\Base\Kneeboards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C4F7E4D-85C2-498B-B7EE-6CA9B1EFE102}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4343C8A1-BE8A-41E2-9D66-0559985224CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5325" yWindow="4635" windowWidth="43200" windowHeight="17145" xr2:uid="{0FCC770A-A480-4475-A2DE-100B627674D7}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="4" xr2:uid="{0FCC770A-A480-4475-A2DE-100B627674D7}"/>
   </bookViews>
   <sheets>
     <sheet name="F4E II" sheetId="20" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="951" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="270">
   <si>
     <t>ARC-186</t>
   </si>
@@ -795,9 +795,6 @@
     <t>joł</t>
   </si>
   <si>
-    <t>KC130 20k</t>
-  </si>
-  <si>
     <t>KC-135 23k</t>
   </si>
   <si>
@@ -856,6 +853,27 @@
   </si>
   <si>
     <t>Oil Instalations</t>
+  </si>
+  <si>
+    <t>EPRO</t>
+  </si>
+  <si>
+    <t>47X</t>
+  </si>
+  <si>
+    <t>BNK</t>
+  </si>
+  <si>
+    <t>171/213'</t>
+  </si>
+  <si>
+    <t>RANGE</t>
+  </si>
+  <si>
+    <t>152/128'</t>
+  </si>
+  <si>
+    <t>165/184'</t>
   </si>
 </sst>
 </file>
@@ -1257,7 +1275,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="248">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -1862,71 +1880,11 @@
     <xf numFmtId="0" fontId="7" fillId="14" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1946,6 +1904,45 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2452,24 +2449,24 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
-        <v>255</v>
-      </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="D3" s="228" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -2501,11 +2498,11 @@
       <c r="F6" s="208" t="s">
         <v>232</v>
       </c>
-      <c r="G6" s="229">
+      <c r="G6" s="88">
         <v>1</v>
       </c>
-      <c r="H6" s="230"/>
-      <c r="I6" s="231"/>
+      <c r="H6" s="216"/>
+      <c r="I6" s="217"/>
     </row>
     <row r="7" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D7" s="89">
@@ -2515,11 +2512,11 @@
         <v>94</v>
       </c>
       <c r="F7" s="163"/>
-      <c r="G7" s="232">
+      <c r="G7" s="89">
         <v>2</v>
       </c>
-      <c r="H7" s="233"/>
-      <c r="I7" s="234"/>
+      <c r="H7" s="90"/>
+      <c r="I7" s="91"/>
     </row>
     <row r="8" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D8" s="89">
@@ -2529,11 +2526,11 @@
         <v>92</v>
       </c>
       <c r="F8" s="163"/>
-      <c r="G8" s="232">
+      <c r="G8" s="89">
         <v>3</v>
       </c>
-      <c r="H8" s="233"/>
-      <c r="I8" s="234"/>
+      <c r="H8" s="90"/>
+      <c r="I8" s="91"/>
     </row>
     <row r="9" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D9" s="89">
@@ -2543,11 +2540,11 @@
         <v>7</v>
       </c>
       <c r="F9" s="209"/>
-      <c r="G9" s="232">
+      <c r="G9" s="89">
         <v>4</v>
       </c>
-      <c r="H9" s="233"/>
-      <c r="I9" s="235"/>
+      <c r="H9" s="90"/>
+      <c r="I9" s="105"/>
     </row>
     <row r="10" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D10" s="89">
@@ -2559,11 +2556,11 @@
       <c r="F10" s="209" t="s">
         <v>129</v>
       </c>
-      <c r="G10" s="232">
+      <c r="G10" s="89">
         <v>5</v>
       </c>
-      <c r="H10" s="233"/>
-      <c r="I10" s="235"/>
+      <c r="H10" s="90"/>
+      <c r="I10" s="105"/>
     </row>
     <row r="11" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D11" s="98">
@@ -2575,11 +2572,11 @@
       <c r="F11" s="210" t="s">
         <v>87</v>
       </c>
-      <c r="G11" s="232">
+      <c r="G11" s="89">
         <v>6</v>
       </c>
-      <c r="H11" s="236"/>
-      <c r="I11" s="237"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="122"/>
     </row>
     <row r="12" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D12" s="89">
@@ -2589,11 +2586,11 @@
         <v>171</v>
       </c>
       <c r="F12" s="163"/>
-      <c r="G12" s="232">
+      <c r="G12" s="89">
         <v>7</v>
       </c>
-      <c r="H12" s="233"/>
-      <c r="I12" s="234"/>
+      <c r="H12" s="90"/>
+      <c r="I12" s="91"/>
     </row>
     <row r="13" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D13" s="106">
@@ -2605,11 +2602,11 @@
       <c r="F13" s="211" t="s">
         <v>134</v>
       </c>
-      <c r="G13" s="232">
+      <c r="G13" s="89">
         <v>8</v>
       </c>
-      <c r="H13" s="233"/>
-      <c r="I13" s="234"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="91"/>
     </row>
     <row r="14" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D14" s="106">
@@ -2621,11 +2618,11 @@
       <c r="F14" s="211" t="s">
         <v>135</v>
       </c>
-      <c r="G14" s="232">
+      <c r="G14" s="89">
         <v>9</v>
       </c>
-      <c r="H14" s="233"/>
-      <c r="I14" s="234"/>
+      <c r="H14" s="90"/>
+      <c r="I14" s="91"/>
     </row>
     <row r="15" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D15" s="106">
@@ -2637,11 +2634,11 @@
       <c r="F15" s="211" t="s">
         <v>136</v>
       </c>
-      <c r="G15" s="232">
+      <c r="G15" s="89">
         <v>10</v>
       </c>
-      <c r="H15" s="233"/>
-      <c r="I15" s="234"/>
+      <c r="H15" s="90"/>
+      <c r="I15" s="91"/>
     </row>
     <row r="16" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D16" s="106">
@@ -2653,12 +2650,12 @@
       <c r="F16" s="211" t="s">
         <v>137</v>
       </c>
-      <c r="G16" s="232">
+      <c r="G16" s="89">
         <v>11</v>
       </c>
-      <c r="H16" s="233"/>
-      <c r="I16" s="234"/>
-      <c r="J16" s="222"/>
+      <c r="H16" s="90"/>
+      <c r="I16" s="91"/>
+      <c r="J16" s="234"/>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D17" s="106">
@@ -2670,12 +2667,12 @@
       <c r="F17" s="211" t="s">
         <v>138</v>
       </c>
-      <c r="G17" s="232">
+      <c r="G17" s="89">
         <v>12</v>
       </c>
-      <c r="H17" s="233"/>
-      <c r="I17" s="234"/>
-      <c r="J17" s="222"/>
+      <c r="H17" s="90"/>
+      <c r="I17" s="91"/>
+      <c r="J17" s="234"/>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -2687,12 +2684,12 @@
       <c r="F18" s="212" t="s">
         <v>147</v>
       </c>
-      <c r="G18" s="232">
+      <c r="G18" s="89">
         <v>13</v>
       </c>
-      <c r="H18" s="236"/>
-      <c r="I18" s="237"/>
-      <c r="J18" s="222"/>
+      <c r="H18" s="121"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="234"/>
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -2704,12 +2701,12 @@
       <c r="F19" s="213" t="s">
         <v>148</v>
       </c>
-      <c r="G19" s="232">
+      <c r="G19" s="89">
         <v>14</v>
       </c>
-      <c r="H19" s="233"/>
-      <c r="I19" s="234"/>
-      <c r="J19" s="222"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="234"/>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D20" s="115">
@@ -2721,11 +2718,11 @@
       <c r="F20" s="214" t="s">
         <v>141</v>
       </c>
-      <c r="G20" s="232">
+      <c r="G20" s="89">
         <v>15</v>
       </c>
-      <c r="H20" s="233"/>
-      <c r="I20" s="234"/>
+      <c r="H20" s="90"/>
+      <c r="I20" s="91"/>
     </row>
     <row r="21" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D21" s="115">
@@ -2737,11 +2734,11 @@
       <c r="F21" s="214" t="s">
         <v>142</v>
       </c>
-      <c r="G21" s="232">
+      <c r="G21" s="89">
         <v>16</v>
       </c>
-      <c r="H21" s="233"/>
-      <c r="I21" s="234"/>
+      <c r="H21" s="90"/>
+      <c r="I21" s="91"/>
     </row>
     <row r="22" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D22" s="115">
@@ -2753,11 +2750,11 @@
       <c r="F22" s="214" t="s">
         <v>143</v>
       </c>
-      <c r="G22" s="232">
+      <c r="G22" s="89">
         <v>17</v>
       </c>
-      <c r="H22" s="233"/>
-      <c r="I22" s="234"/>
+      <c r="H22" s="90"/>
+      <c r="I22" s="91"/>
     </row>
     <row r="23" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D23" s="206">
@@ -2769,31 +2766,31 @@
       <c r="F23" s="215" t="s">
         <v>144</v>
       </c>
-      <c r="G23" s="232">
+      <c r="G23" s="89">
         <v>18</v>
       </c>
-      <c r="H23" s="233"/>
-      <c r="I23" s="234"/>
+      <c r="H23" s="90"/>
+      <c r="I23" s="91"/>
     </row>
     <row r="24" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D24" s="121"/>
       <c r="E24" s="90"/>
       <c r="F24" s="163"/>
-      <c r="G24" s="232">
+      <c r="G24" s="89">
         <v>19</v>
       </c>
-      <c r="H24" s="233"/>
-      <c r="I24" s="234"/>
+      <c r="H24" s="90"/>
+      <c r="I24" s="91"/>
     </row>
     <row r="25" spans="3:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D25" s="121"/>
       <c r="E25" s="90"/>
       <c r="F25" s="163"/>
-      <c r="G25" s="232">
+      <c r="G25" s="89">
         <v>20</v>
       </c>
-      <c r="H25" s="233"/>
-      <c r="I25" s="234"/>
+      <c r="H25" s="90"/>
+      <c r="I25" s="91"/>
     </row>
     <row r="26" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D26" s="51"/>
@@ -2823,10 +2820,10 @@
       <c r="E29" s="150"/>
       <c r="F29" s="150"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D30" s="149" t="s">
@@ -2863,46 +2860,46 @@
       <c r="I32" s="87"/>
     </row>
     <row r="33" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D33" s="238" t="s">
+      <c r="D33" s="218" t="s">
+        <v>255</v>
+      </c>
+      <c r="E33" s="219" t="s">
+        <v>224</v>
+      </c>
+      <c r="F33" s="220"/>
+      <c r="G33" s="221"/>
+      <c r="H33" s="222"/>
+      <c r="I33" s="87"/>
+    </row>
+    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
+      <c r="D34" s="223" t="s">
         <v>256</v>
       </c>
-      <c r="E33" s="239" t="s">
-        <v>224</v>
-      </c>
-      <c r="F33" s="240"/>
-      <c r="G33" s="241"/>
-      <c r="H33" s="242"/>
-      <c r="I33" s="87"/>
-    </row>
-    <row r="34" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D34" s="243" t="s">
+      <c r="E34" s="219" t="s">
+        <v>258</v>
+      </c>
+      <c r="F34" s="227" t="s">
+        <v>262</v>
+      </c>
+      <c r="G34" s="221"/>
+      <c r="H34" s="221"/>
+      <c r="I34" s="5"/>
+    </row>
+    <row r="35" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D35" s="224" t="s">
         <v>257</v>
       </c>
-      <c r="E34" s="239" t="s">
+      <c r="E35" s="225" t="s">
         <v>259</v>
       </c>
-      <c r="F34" s="247" t="s">
-        <v>263</v>
-      </c>
-      <c r="G34" s="241"/>
-      <c r="H34" s="241"/>
-      <c r="I34" s="5"/>
-    </row>
-    <row r="35" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D35" s="244" t="s">
-        <v>258</v>
-      </c>
-      <c r="E35" s="245" t="s">
+      <c r="F35" s="225" t="s">
         <v>260</v>
       </c>
-      <c r="F35" s="245" t="s">
+      <c r="G35" s="226" t="s">
+        <v>82</v>
+      </c>
+      <c r="H35" s="226" t="s">
         <v>261</v>
-      </c>
-      <c r="G35" s="246" t="s">
-        <v>82</v>
-      </c>
-      <c r="H35" s="246" t="s">
-        <v>262</v>
       </c>
       <c r="I35" s="139"/>
     </row>
@@ -2940,24 +2937,24 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>178</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="155" t="s">
@@ -3094,7 +3091,7 @@
       <c r="G16" s="89"/>
       <c r="H16" s="90"/>
       <c r="I16" s="92"/>
-      <c r="J16" s="225"/>
+      <c r="J16" s="237"/>
     </row>
     <row r="17" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D17" s="89"/>
@@ -3103,7 +3100,7 @@
       <c r="G17" s="89"/>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="225"/>
+      <c r="J17" s="237"/>
     </row>
     <row r="18" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D18" s="89"/>
@@ -3112,7 +3109,7 @@
       <c r="G18" s="89"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="225"/>
+      <c r="J18" s="237"/>
     </row>
     <row r="19" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D19" s="89"/>
@@ -3121,7 +3118,7 @@
       <c r="G19" s="89"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91"/>
-      <c r="J19" s="225"/>
+      <c r="J19" s="237"/>
     </row>
     <row r="20" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D20" s="89"/>
@@ -3199,10 +3196,10 @@
       <c r="E29" s="150"/>
       <c r="F29" s="150"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D30" s="149" t="s">
@@ -3281,24 +3278,24 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>173</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="155" t="s">
@@ -3463,7 +3460,7 @@
       <c r="G16" s="89"/>
       <c r="H16" s="90"/>
       <c r="I16" s="92"/>
-      <c r="J16" s="225"/>
+      <c r="J16" s="237"/>
     </row>
     <row r="17" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D17" s="156">
@@ -3478,7 +3475,7 @@
       <c r="G17" s="89"/>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="225"/>
+      <c r="J17" s="237"/>
     </row>
     <row r="18" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -3493,7 +3490,7 @@
       <c r="G18" s="89"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="225"/>
+      <c r="J18" s="237"/>
     </row>
     <row r="19" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -3508,7 +3505,7 @@
       <c r="G19" s="89"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91"/>
-      <c r="J19" s="225"/>
+      <c r="J19" s="237"/>
     </row>
     <row r="20" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D20" s="128">
@@ -3620,10 +3617,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D30" s="50"/>
@@ -3696,24 +3693,24 @@
   <sheetData>
     <row r="2" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -4061,10 +4058,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D30" s="50" t="s">
@@ -4132,24 +4129,24 @@
   <sheetData>
     <row r="2" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="57" t="s">
@@ -4460,10 +4457,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D30" s="50" t="s">
@@ -4533,24 +4530,24 @@
   <sheetData>
     <row r="2" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>24</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -4905,10 +4902,10 @@
       <c r="E29" s="38"/>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D30" s="50" t="s">
@@ -4982,29 +4979,29 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
-        <v>247</v>
-      </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="D3" s="228" t="s">
+        <v>246</v>
+      </c>
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41"/>
       <c r="E5" s="41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F5" s="43"/>
       <c r="G5" s="41"/>
@@ -5033,7 +5030,7 @@
         <v>71</v>
       </c>
       <c r="F7" s="199" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G7" s="89"/>
       <c r="H7" s="90"/>
@@ -5047,7 +5044,7 @@
         <v>32</v>
       </c>
       <c r="F8" s="199" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G8" s="89"/>
       <c r="H8" s="90"/>
@@ -5156,7 +5153,7 @@
       <c r="G16" s="89"/>
       <c r="H16" s="90"/>
       <c r="I16" s="92"/>
-      <c r="J16" s="225"/>
+      <c r="J16" s="237"/>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D17" s="106">
@@ -5171,7 +5168,7 @@
       <c r="G17" s="89"/>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="225"/>
+      <c r="J17" s="237"/>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -5186,7 +5183,7 @@
       <c r="G18" s="89"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="225"/>
+      <c r="J18" s="237"/>
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -5201,7 +5198,7 @@
       <c r="G19" s="89"/>
       <c r="H19" s="90"/>
       <c r="I19" s="91"/>
-      <c r="J19" s="225"/>
+      <c r="J19" s="237"/>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D20" s="115">
@@ -5313,10 +5310,10 @@
       <c r="E29" s="150"/>
       <c r="F29" s="150"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D30" s="149" t="s">
@@ -5397,24 +5394,24 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -5652,7 +5649,7 @@
       <c r="I16" s="92" t="s">
         <v>151</v>
       </c>
-      <c r="J16" s="225"/>
+      <c r="J16" s="237"/>
     </row>
     <row r="17" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D17" s="106">
@@ -5673,7 +5670,7 @@
       <c r="I17" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="J17" s="225"/>
+      <c r="J17" s="237"/>
     </row>
     <row r="18" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -5694,7 +5691,7 @@
       <c r="I18" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="J18" s="225"/>
+      <c r="J18" s="237"/>
     </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -5715,7 +5712,7 @@
       <c r="I19" s="108" t="s">
         <v>134</v>
       </c>
-      <c r="J19" s="225"/>
+      <c r="J19" s="237"/>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D20" s="93">
@@ -5866,10 +5863,10 @@
       <c r="E29" s="132"/>
       <c r="F29" s="132"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D30" s="133" t="s">
@@ -5982,24 +5979,24 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -6232,7 +6229,7 @@
       <c r="I16" s="92" t="s">
         <v>151</v>
       </c>
-      <c r="J16" s="225"/>
+      <c r="J16" s="237"/>
     </row>
     <row r="17" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D17" s="106">
@@ -6253,7 +6250,7 @@
       <c r="I17" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="J17" s="225"/>
+      <c r="J17" s="237"/>
     </row>
     <row r="18" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -6274,7 +6271,7 @@
       <c r="I18" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="J18" s="225"/>
+      <c r="J18" s="237"/>
     </row>
     <row r="19" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -6293,7 +6290,7 @@
         <v>165</v>
       </c>
       <c r="I19" s="91"/>
-      <c r="J19" s="225"/>
+      <c r="J19" s="237"/>
     </row>
     <row r="20" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D20" s="115">
@@ -6431,10 +6428,10 @@
       <c r="E29" s="150"/>
       <c r="F29" s="150"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="3:14" x14ac:dyDescent="0.25">
       <c r="D30" s="149" t="s">
@@ -6521,37 +6518,37 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>220</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="226" t="s">
+      <c r="D5" s="238" t="s">
         <v>209</v>
       </c>
-      <c r="E5" s="227"/>
+      <c r="E5" s="239"/>
       <c r="F5" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="G5" s="226" t="s">
+      <c r="G5" s="238" t="s">
         <v>210</v>
       </c>
-      <c r="H5" s="227"/>
+      <c r="H5" s="239"/>
       <c r="I5" s="43" t="s">
         <v>212</v>
       </c>
@@ -6776,7 +6773,7 @@
       <c r="I16" s="92" t="s">
         <v>151</v>
       </c>
-      <c r="J16" s="225"/>
+      <c r="J16" s="237"/>
     </row>
     <row r="17" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D17" s="106">
@@ -6797,7 +6794,7 @@
       <c r="I17" s="91" t="s">
         <v>152</v>
       </c>
-      <c r="J17" s="225"/>
+      <c r="J17" s="237"/>
     </row>
     <row r="18" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D18" s="123">
@@ -6818,7 +6815,7 @@
       <c r="I18" s="91" t="s">
         <v>153</v>
       </c>
-      <c r="J18" s="225"/>
+      <c r="J18" s="237"/>
     </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D19" s="123">
@@ -6839,7 +6836,7 @@
       <c r="I19" s="108" t="s">
         <v>134</v>
       </c>
-      <c r="J19" s="225"/>
+      <c r="J19" s="237"/>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D20" s="93">
@@ -6985,31 +6982,39 @@
         <v>22</v>
       </c>
       <c r="H27" s="157" t="s">
-        <v>159</v>
+        <v>6</v>
       </c>
       <c r="I27" s="158" t="s">
-        <v>202</v>
+        <v>263</v>
       </c>
       <c r="T27" s="85"/>
     </row>
     <row r="28" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="D28" s="51"/>
-      <c r="E28" s="12"/>
+      <c r="D28" s="51" t="s">
+        <v>264</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>265</v>
+      </c>
       <c r="F28" s="53"/>
       <c r="G28" s="181">
         <v>23</v>
       </c>
       <c r="H28" s="157" t="s">
-        <v>160</v>
+        <v>71</v>
       </c>
       <c r="I28" s="158" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="T28" s="85"/>
     </row>
     <row r="29" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="D29" s="51"/>
-      <c r="E29" s="12"/>
+      <c r="D29" s="51" t="s">
+        <v>239</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>266</v>
+      </c>
       <c r="F29" s="53"/>
       <c r="G29" s="181">
         <v>24</v>
@@ -7023,8 +7028,12 @@
       <c r="T29" s="85"/>
     </row>
     <row r="30" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="D30" s="51"/>
-      <c r="E30" s="12"/>
+      <c r="D30" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>268</v>
+      </c>
       <c r="F30" s="53"/>
       <c r="G30" s="181">
         <v>25</v>
@@ -7038,8 +7047,12 @@
       <c r="T30" s="85"/>
     </row>
     <row r="31" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="D31" s="51"/>
-      <c r="E31" s="12"/>
+      <c r="D31" s="51" t="s">
+        <v>240</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>269</v>
+      </c>
       <c r="F31" s="53"/>
       <c r="G31" s="181">
         <v>26</v>
@@ -7118,10 +7131,10 @@
       <c r="E37" s="132"/>
       <c r="F37" s="132"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="223" t="s">
+      <c r="H37" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="224"/>
+      <c r="I37" s="236"/>
     </row>
     <row r="38" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D38" s="133" t="s">
@@ -7155,9 +7168,6 @@
       </c>
       <c r="E40" s="141"/>
       <c r="F40" s="142"/>
-      <c r="G40" t="s">
-        <v>194</v>
-      </c>
       <c r="H40" s="189" t="s">
         <v>223</v>
       </c>
@@ -7169,9 +7179,6 @@
       </c>
       <c r="E41" s="141"/>
       <c r="F41" s="142"/>
-      <c r="G41" t="s">
-        <v>243</v>
-      </c>
       <c r="H41" s="190" t="s">
         <v>224</v>
       </c>
@@ -7197,9 +7204,7 @@
       <c r="I43" s="183"/>
     </row>
     <row r="44" spans="4:20" x14ac:dyDescent="0.25">
-      <c r="D44" s="149" t="s">
-        <v>234</v>
-      </c>
+      <c r="D44" s="149"/>
       <c r="E44" s="151"/>
       <c r="F44" s="151"/>
       <c r="H44" s="190" t="s">
@@ -7208,9 +7213,7 @@
       <c r="I44" s="191"/>
     </row>
     <row r="45" spans="4:20" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D45" s="185" t="s">
-        <v>235</v>
-      </c>
+      <c r="D45" s="185"/>
       <c r="E45" s="186"/>
       <c r="F45" s="186"/>
       <c r="G45" s="187" t="s">
@@ -7230,7 +7233,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="6" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -7249,24 +7252,24 @@
   <sheetData>
     <row r="2" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>228</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:12" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -7862,13 +7865,13 @@
       <c r="E28" s="150"/>
       <c r="F28" s="150"/>
       <c r="G28" s="1"/>
-      <c r="H28" s="223" t="s">
+      <c r="H28" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I28" s="224"/>
+      <c r="I28" s="236"/>
       <c r="J28" s="2"/>
-      <c r="K28" s="228"/>
-      <c r="L28" s="228"/>
+      <c r="K28" s="240"/>
+      <c r="L28" s="240"/>
     </row>
     <row r="29" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D29" s="149" t="s">
@@ -7904,7 +7907,7 @@
       <c r="E31" s="153"/>
       <c r="F31" s="154"/>
       <c r="G31" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H31" s="86"/>
       <c r="I31" s="87"/>
@@ -7978,29 +7981,29 @@
   <sheetData>
     <row r="2" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:9" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>35</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216"/>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="E3" s="229"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
         <v>37</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F5" s="43"/>
       <c r="G5" s="70" t="s">
@@ -8023,7 +8026,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="201" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="I6" s="202" t="s">
         <v>240</v>
@@ -8041,7 +8044,7 @@
         <v>2</v>
       </c>
       <c r="H7" s="204" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I7" s="205" t="s">
         <v>239</v>
@@ -8155,7 +8158,7 @@
         <v>9</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I14" s="9"/>
     </row>
@@ -8171,7 +8174,7 @@
         <v>10</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I15" s="10"/>
     </row>
@@ -8298,14 +8301,14 @@
         <v>221</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F29" s="38"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="223" t="s">
+      <c r="H29" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I29" s="224"/>
+      <c r="I29" s="236"/>
     </row>
     <row r="30" spans="4:9" x14ac:dyDescent="0.25">
       <c r="D30" s="50" t="s">
@@ -8381,30 +8384,30 @@
   <sheetData>
     <row r="2" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:12" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>186</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="220"/>
-      <c r="J3" s="220"/>
-      <c r="K3" s="220"/>
-      <c r="L3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="232"/>
+      <c r="J3" s="232"/>
+      <c r="K3" s="232"/>
+      <c r="L3" s="229"/>
     </row>
     <row r="4" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="221"/>
-      <c r="J4" s="221"/>
-      <c r="K4" s="221"/>
-      <c r="L4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="231"/>
     </row>
     <row r="5" spans="4:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D5" s="41" t="s">
@@ -9057,7 +9060,7 @@
       <c r="L27" s="130" t="s">
         <v>141</v>
       </c>
-      <c r="M27" s="225"/>
+      <c r="M27" s="237"/>
     </row>
     <row r="28" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D28" s="128">
@@ -9087,7 +9090,7 @@
       <c r="L28" s="130" t="s">
         <v>142</v>
       </c>
-      <c r="M28" s="225"/>
+      <c r="M28" s="237"/>
     </row>
     <row r="29" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D29" s="128">
@@ -9117,7 +9120,7 @@
       <c r="L29" s="130" t="s">
         <v>143</v>
       </c>
-      <c r="M29" s="225"/>
+      <c r="M29" s="237"/>
     </row>
     <row r="30" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D30" s="128">
@@ -9147,7 +9150,7 @@
       <c r="L30" s="130" t="s">
         <v>144</v>
       </c>
-      <c r="M30" s="225"/>
+      <c r="M30" s="237"/>
     </row>
     <row r="31" spans="4:13" x14ac:dyDescent="0.25">
       <c r="D31" s="128">
@@ -9278,10 +9281,10 @@
       <c r="H39" s="38"/>
       <c r="I39" s="38"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="223" t="s">
+      <c r="K39" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="L39" s="224"/>
+      <c r="L39" s="236"/>
     </row>
     <row r="40" spans="4:12" x14ac:dyDescent="0.25">
       <c r="D40" s="133" t="s">
@@ -9326,7 +9329,7 @@
       <c r="E43" s="141"/>
       <c r="F43" s="142"/>
       <c r="G43" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H43" s="28"/>
       <c r="I43" s="28"/>
@@ -9432,37 +9435,37 @@
   <sheetData>
     <row r="2" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D3" s="216" t="s">
+      <c r="D3" s="228" t="s">
         <v>213</v>
       </c>
-      <c r="E3" s="217"/>
-      <c r="F3" s="216" t="s">
+      <c r="E3" s="229"/>
+      <c r="F3" s="228" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="220"/>
-      <c r="H3" s="220"/>
-      <c r="I3" s="217"/>
+      <c r="G3" s="232"/>
+      <c r="H3" s="232"/>
+      <c r="I3" s="229"/>
     </row>
     <row r="4" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D4" s="218"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="218"/>
-      <c r="G4" s="221"/>
-      <c r="H4" s="221"/>
-      <c r="I4" s="219"/>
+      <c r="D4" s="230"/>
+      <c r="E4" s="231"/>
+      <c r="F4" s="230"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="231"/>
     </row>
     <row r="5" spans="4:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D5" s="226" t="s">
+      <c r="D5" s="238" t="s">
         <v>214</v>
       </c>
-      <c r="E5" s="227"/>
+      <c r="E5" s="239"/>
       <c r="F5" s="43" t="s">
         <v>217</v>
       </c>
-      <c r="G5" s="226" t="s">
+      <c r="G5" s="238" t="s">
         <v>215</v>
       </c>
-      <c r="H5" s="227"/>
+      <c r="H5" s="239"/>
       <c r="I5" s="43" t="s">
         <v>216</v>
       </c>
@@ -9583,7 +9586,7 @@
       <c r="G16" s="89"/>
       <c r="H16" s="90"/>
       <c r="I16" s="92"/>
-      <c r="J16" s="225"/>
+      <c r="J16" s="237"/>
     </row>
     <row r="17" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D17" s="106"/>
@@ -9592,7 +9595,7 @@
       <c r="G17" s="89"/>
       <c r="H17" s="90"/>
       <c r="I17" s="91"/>
-      <c r="J17" s="225"/>
+      <c r="J17" s="237"/>
     </row>
     <row r="18" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D18" s="123"/>
@@ -9601,7 +9604,7 @@
       <c r="G18" s="89"/>
       <c r="H18" s="90"/>
       <c r="I18" s="91"/>
-      <c r="J18" s="225"/>
+      <c r="J18" s="237"/>
     </row>
     <row r="19" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D19" s="123"/>
@@ -9610,7 +9613,7 @@
       <c r="G19" s="106"/>
       <c r="H19" s="107"/>
       <c r="I19" s="108"/>
-      <c r="J19" s="225"/>
+      <c r="J19" s="237"/>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D20" s="93"/>
@@ -9761,10 +9764,10 @@
       <c r="E37" s="132"/>
       <c r="F37" s="132"/>
       <c r="G37" s="1"/>
-      <c r="H37" s="223" t="s">
+      <c r="H37" s="235" t="s">
         <v>25</v>
       </c>
-      <c r="I37" s="224"/>
+      <c r="I37" s="236"/>
     </row>
     <row r="38" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D38" s="133" t="s">
